--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120970201</v>
+        <v>120970196</v>
       </c>
       <c r="B2" t="n">
-        <v>105176</v>
+        <v>100347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -723,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580515</v>
+        <v>580664</v>
       </c>
       <c r="R2" t="n">
-        <v>6526993</v>
+        <v>6527008</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -758,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120970198</v>
+        <v>120970199</v>
       </c>
       <c r="B3" t="n">
-        <v>100337</v>
+        <v>100347</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -874,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120970196</v>
+        <v>120970203</v>
       </c>
       <c r="B4" t="n">
-        <v>100337</v>
+        <v>105186</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,24 +923,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580664</v>
+        <v>580582</v>
       </c>
       <c r="R4" t="n">
-        <v>6527008</v>
+        <v>6526995</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -990,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,10 +1027,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120970203</v>
+        <v>120970201</v>
       </c>
       <c r="B5" t="n">
-        <v>105176</v>
+        <v>105186</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580582</v>
+        <v>580515</v>
       </c>
       <c r="R5" t="n">
-        <v>6526995</v>
+        <v>6526993</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,7 +1150,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103119</v>
+        <v>103129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120970196</v>
+        <v>120970201</v>
       </c>
       <c r="B2" t="n">
-        <v>100347</v>
+        <v>105186</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>580664</v>
+        <v>580515</v>
       </c>
       <c r="R2" t="n">
-        <v>6527008</v>
+        <v>6526993</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -754,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1027,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120970201</v>
+        <v>120970196</v>
       </c>
       <c r="B5" t="n">
-        <v>105186</v>
+        <v>100347</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,28 +1047,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580515</v>
+        <v>580664</v>
       </c>
       <c r="R5" t="n">
-        <v>6526993</v>
+        <v>6527008</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120970201</v>
+        <v>120970200</v>
       </c>
       <c r="B2" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,10 +710,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -758,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -768,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,7 +802,7 @@
         <v>120970199</v>
       </c>
       <c r="B3" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -914,7 +918,7 @@
         <v>120970203</v>
       </c>
       <c r="B4" t="n">
-        <v>105186</v>
+        <v>105199</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1034,7 +1038,7 @@
         <v>120970196</v>
       </c>
       <c r="B5" t="n">
-        <v>100347</v>
+        <v>100360</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1150,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103129</v>
+        <v>103142</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103142</v>
+        <v>103143</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103143</v>
+        <v>103146</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103146</v>
+        <v>103152</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103152</v>
+        <v>103153</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 51852-2019 artfynd.xlsx
+++ b/artfynd/A 51852-2019 artfynd.xlsx
@@ -1154,7 +1154,7 @@
         <v>121320307</v>
       </c>
       <c r="B6" t="n">
-        <v>103153</v>
+        <v>103161</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
